--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1806.8</v>
+        <v>1788.78</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9357.610000000001</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,68 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1074.15</v>
+        <v>1061.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1443565-35-CM26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>20457.74</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -755,6 +755,128 @@
         <v>20457.74</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1443565-36-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>3065.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1443565-45-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>408.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hugo Pascual Paco Bolaños</t>
+          <t>HUGO PASCUAL PACO BOLAÑOS</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -877,6 +877,128 @@
         <v>408.91</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5952-178-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7.115.014-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>305.61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5952-179-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7.115.014-3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>203.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5602-184-CM26</t>
+          <t>5965-193-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9303.450000000001</v>
+        <v>656.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5952-97-CM26</t>
+          <t>5602-184-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HUGO PASCUAL PACO BOLAÑOS</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.472.608-9</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1061.65</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1443565-35-CM26</t>
+          <t>5952-97-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>HUGO PASCUAL PACO BOLAÑOS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>10.472.608-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>20457.74</v>
+        <v>1061.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1443565-36-CM26</t>
+          <t>1443565-35-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3065.85</v>
+        <v>20457.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1443565-45-CM26</t>
+          <t>1443565-36-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>408.91</v>
+        <v>3065.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5952-178-CM26</t>
+          <t>1443565-45-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.115.014-3</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>305.61</v>
+        <v>408.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5952-179-CM26</t>
+          <t>5952-178-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,6 +996,67 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>305.61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5952-179-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7.115.014-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>203.74</v>
       </c>
     </row>
